--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="102">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -184,6 +184,48 @@
   </si>
   <si>
     <t>Serotonin [Mass/time] in 24 hour Urine</t>
+  </si>
+  <si>
+    <t>27057-9</t>
+  </si>
+  <si>
+    <t>Serotonin [Mass/volume] in Serum</t>
+  </si>
+  <si>
+    <t>2940-5</t>
+  </si>
+  <si>
+    <t>Serotonin [Mass/volume] in Plasma</t>
+  </si>
+  <si>
+    <t>2939-7</t>
+  </si>
+  <si>
+    <t>Serotonin [Mass/volume] in Blood</t>
+  </si>
+  <si>
+    <t>1695-6</t>
+  </si>
+  <si>
+    <t>5-Hydroxyindoleacetate [Mass/time] in 24 hour Urine</t>
+  </si>
+  <si>
+    <t>31203-3</t>
+  </si>
+  <si>
+    <t>5-Hydroxyindoleacetate [Mass/volume] in 24 hour Urine</t>
+  </si>
+  <si>
+    <t>1694-9</t>
+  </si>
+  <si>
+    <t>5-Hydroxyindoleacetate [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>44288-9</t>
+  </si>
+  <si>
+    <t>5-Hydroxyindoleacetate/Creatinine [Mass Ratio] in 24 hour Urine</t>
   </si>
   <si>
     <t>2141-0</t>
@@ -540,7 +582,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -784,15 +826,71 @@
         <v>85</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="128">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -246,16 +246,94 @@
     <t>Homovanillate [Mass/time] in 24 hour Urine</t>
   </si>
   <si>
+    <t>53595-5</t>
+  </si>
+  <si>
+    <t>Homovanillate [Mass/volume] in 24 hour Urine</t>
+  </si>
+  <si>
+    <t>13760-4</t>
+  </si>
+  <si>
+    <t>Homovanillate/Creatinine [Mass Ratio] in 24 hour Urine</t>
+  </si>
+  <si>
+    <t>11146-8</t>
+  </si>
+  <si>
+    <t>Homovanillate/Creatinine [Mass Ratio] in Urine</t>
+  </si>
+  <si>
     <t>3122-9</t>
   </si>
   <si>
     <t>Vanillylmandelate [Mass/time] in 24 hour Urine</t>
   </si>
   <si>
+    <t>26706-2</t>
+  </si>
+  <si>
+    <t>Vanillylmandelate [Mass/volume] in 24 hour Urine</t>
+  </si>
+  <si>
+    <t>30571-4</t>
+  </si>
+  <si>
+    <t>Vanillylmandelate/Creatinine [Mass Ratio] in 24 hour Urine</t>
+  </si>
+  <si>
+    <t>3124-5</t>
+  </si>
+  <si>
+    <t>Vanillylmandelate/Creatinine [Mass Ratio] in Urine</t>
+  </si>
+  <si>
     <t>27055-3</t>
   </si>
   <si>
     <t>Catecholamines Free [Mass/time] in 24 hour Urine</t>
+  </si>
+  <si>
+    <t>2058-6</t>
+  </si>
+  <si>
+    <t>Catecholamines [Mass/time] in 24 hour Urine</t>
+  </si>
+  <si>
+    <t>2056-0</t>
+  </si>
+  <si>
+    <t>Catecholamines [Mass/volume] in Plasma</t>
+  </si>
+  <si>
+    <t>43108-0</t>
+  </si>
+  <si>
+    <t>Metanephrine and Normetanephrine panel [Mass/volume] - Serum or Plasma</t>
+  </si>
+  <si>
+    <t>57462-4</t>
+  </si>
+  <si>
+    <t>Normetanephrine Free [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2669-0</t>
+  </si>
+  <si>
+    <t>Normetanephrine [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2609-6</t>
+  </si>
+  <si>
+    <t>Metanephrines [Mass/time] in 24 hour Urine</t>
+  </si>
+  <si>
+    <t>2671-6</t>
+  </si>
+  <si>
+    <t>Normetanephrine [Mass/time] in 24 hour Urine</t>
   </si>
   <si>
     <t>2842-3</t>
@@ -582,7 +660,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -882,15 +960,119 @@
         <v>99</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tumormarker-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
